--- a/data/nzd0122/nzd0122.xlsx
+++ b/data/nzd0122/nzd0122.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y284"/>
+  <dimension ref="A1:Y287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23439,6 +23439,249 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:05:43+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="C285" t="n">
+        <v>344.62</v>
+      </c>
+      <c r="D285" t="n">
+        <v>342.02</v>
+      </c>
+      <c r="E285" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="F285" t="n">
+        <v>361</v>
+      </c>
+      <c r="G285" t="n">
+        <v>363.57</v>
+      </c>
+      <c r="H285" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="I285" t="n">
+        <v>346.91</v>
+      </c>
+      <c r="J285" t="n">
+        <v>351.98</v>
+      </c>
+      <c r="K285" t="n">
+        <v>407.95</v>
+      </c>
+      <c r="L285" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="M285" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="N285" t="n">
+        <v>358.44</v>
+      </c>
+      <c r="O285" t="n">
+        <v>359.97</v>
+      </c>
+      <c r="P285" t="n">
+        <v>366.91</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="R285" t="n">
+        <v>362.44</v>
+      </c>
+      <c r="S285" t="n">
+        <v>359.71</v>
+      </c>
+      <c r="T285" t="n">
+        <v>364.65</v>
+      </c>
+      <c r="U285" t="n">
+        <v>372.35</v>
+      </c>
+      <c r="V285" t="n">
+        <v>376.04</v>
+      </c>
+      <c r="W285" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="X285" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="C286" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="D286" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="E286" t="n">
+        <v>355.92</v>
+      </c>
+      <c r="F286" t="n">
+        <v>362.54</v>
+      </c>
+      <c r="G286" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="H286" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="I286" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="J286" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="K286" t="n">
+        <v>407.95</v>
+      </c>
+      <c r="L286" t="n">
+        <v>359.54</v>
+      </c>
+      <c r="M286" t="n">
+        <v>359.15</v>
+      </c>
+      <c r="N286" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="O286" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="P286" t="n">
+        <v>369.98</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="R286" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="S286" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="T286" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="U286" t="n">
+        <v>376.05</v>
+      </c>
+      <c r="V286" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="W286" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="X286" t="n">
+        <v>378.32</v>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>361.09</v>
+      </c>
+      <c r="C287" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="D287" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="E287" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="F287" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="G287" t="n">
+        <v>365.66</v>
+      </c>
+      <c r="H287" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="I287" t="n">
+        <v>351.74</v>
+      </c>
+      <c r="J287" t="n">
+        <v>359.66</v>
+      </c>
+      <c r="K287" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="L287" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="M287" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="N287" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="O287" t="n">
+        <v>363.54</v>
+      </c>
+      <c r="P287" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="R287" t="n">
+        <v>365.84</v>
+      </c>
+      <c r="S287" t="n">
+        <v>364.04</v>
+      </c>
+      <c r="T287" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="U287" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="V287" t="n">
+        <v>381.14</v>
+      </c>
+      <c r="W287" t="n">
+        <v>373.32</v>
+      </c>
+      <c r="X287" t="n">
+        <v>381.27</v>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23450,7 +23693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26353,6 +26596,36 @@
       </c>
       <c r="B290" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -26521,28 +26794,28 @@
         <v>0.1526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2121935860378066</v>
+        <v>0.2162976064563276</v>
       </c>
       <c r="J2" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K2" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05838937228500274</v>
+        <v>0.0618155308876287</v>
       </c>
       <c r="M2" t="n">
-        <v>4.71410695592335</v>
+        <v>4.686325807317202</v>
       </c>
       <c r="N2" t="n">
-        <v>35.98949246841795</v>
+        <v>35.64667182084131</v>
       </c>
       <c r="O2" t="n">
-        <v>5.99912430846519</v>
+        <v>5.97048338251111</v>
       </c>
       <c r="P2" t="n">
-        <v>353.0509370679649</v>
+        <v>353.0044821078856</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26599,28 +26872,28 @@
         <v>0.1234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2073280738833933</v>
+        <v>0.1932667319874243</v>
       </c>
       <c r="J3" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K3" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06476113973922082</v>
+        <v>0.05721118896039945</v>
       </c>
       <c r="M3" t="n">
-        <v>4.678091324547178</v>
+        <v>4.689758155908865</v>
       </c>
       <c r="N3" t="n">
-        <v>30.76790733251926</v>
+        <v>30.90100308300362</v>
       </c>
       <c r="O3" t="n">
-        <v>5.546882667996436</v>
+        <v>5.558867068297606</v>
       </c>
       <c r="P3" t="n">
-        <v>343.5151530854199</v>
+        <v>343.6743494201362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26677,28 +26950,28 @@
         <v>0.1286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1428237570063255</v>
+        <v>0.1292129918410563</v>
       </c>
       <c r="J4" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K4" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01822198989774315</v>
+        <v>0.01520323111302724</v>
       </c>
       <c r="M4" t="n">
-        <v>6.07161662489025</v>
+        <v>6.063260585973384</v>
       </c>
       <c r="N4" t="n">
-        <v>54.4743525745826</v>
+        <v>54.29352100625245</v>
       </c>
       <c r="O4" t="n">
-        <v>7.380674262869389</v>
+        <v>7.368413737450717</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9866274350089</v>
+        <v>345.1406640813154</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26755,28 +27028,28 @@
         <v>0.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1122539899385226</v>
+        <v>0.1118275268223622</v>
       </c>
       <c r="J5" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K5" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01026947054198257</v>
+        <v>0.01042982217081856</v>
       </c>
       <c r="M5" t="n">
-        <v>6.355962706874842</v>
+        <v>6.295670248702931</v>
       </c>
       <c r="N5" t="n">
-        <v>60.19302348976603</v>
+        <v>59.56512535681492</v>
       </c>
       <c r="O5" t="n">
-        <v>7.758416300364788</v>
+        <v>7.71784460564055</v>
       </c>
       <c r="P5" t="n">
-        <v>352.9464963386448</v>
+        <v>352.9512997030873</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26833,28 +27106,28 @@
         <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.170218385174499</v>
+        <v>0.1595183725551739</v>
       </c>
       <c r="J6" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K6" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02168239319976228</v>
+        <v>0.01946218674796718</v>
       </c>
       <c r="M6" t="n">
-        <v>6.446581917992898</v>
+        <v>6.422506658269092</v>
       </c>
       <c r="N6" t="n">
-        <v>64.79765037228385</v>
+        <v>64.36044765669708</v>
       </c>
       <c r="O6" t="n">
-        <v>8.049698775251398</v>
+        <v>8.022496348188454</v>
       </c>
       <c r="P6" t="n">
-        <v>362.0127855371423</v>
+        <v>362.1338811031481</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26911,28 +27184,28 @@
         <v>0.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1528638921263973</v>
+        <v>0.1432264248448274</v>
       </c>
       <c r="J7" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K7" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02074196979810006</v>
+        <v>0.01860976619596655</v>
       </c>
       <c r="M7" t="n">
-        <v>5.872713782749094</v>
+        <v>5.852571292706463</v>
       </c>
       <c r="N7" t="n">
-        <v>54.68026900708458</v>
+        <v>54.30902956492452</v>
       </c>
       <c r="O7" t="n">
-        <v>7.394610808357974</v>
+        <v>7.369466029837204</v>
       </c>
       <c r="P7" t="n">
-        <v>364.6657591815521</v>
+        <v>364.7748158210607</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26989,28 +27262,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1384309809505407</v>
+        <v>0.1349249146978202</v>
       </c>
       <c r="J8" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K8" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01744020699979754</v>
+        <v>0.01695908150717396</v>
       </c>
       <c r="M8" t="n">
-        <v>6.117454405396753</v>
+        <v>6.067267703402514</v>
       </c>
       <c r="N8" t="n">
-        <v>53.48713009340991</v>
+        <v>52.95539081252102</v>
       </c>
       <c r="O8" t="n">
-        <v>7.313489597545751</v>
+        <v>7.277045472753418</v>
       </c>
       <c r="P8" t="n">
-        <v>354.1511750087695</v>
+        <v>354.1908008413924</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27067,28 +27340,28 @@
         <v>0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1451366345248174</v>
+        <v>0.1369343631424338</v>
       </c>
       <c r="J9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K9" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01723749778882433</v>
+        <v>0.01568398149985228</v>
       </c>
       <c r="M9" t="n">
-        <v>6.366898020375102</v>
+        <v>6.332355904916044</v>
       </c>
       <c r="N9" t="n">
-        <v>59.49819634043914</v>
+        <v>59.05541546280696</v>
       </c>
       <c r="O9" t="n">
-        <v>7.713507395500385</v>
+        <v>7.684752140622816</v>
       </c>
       <c r="P9" t="n">
-        <v>349.2505218432668</v>
+        <v>349.3432136882598</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27145,28 +27418,28 @@
         <v>0.1145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0280730236335541</v>
+        <v>0.02442297896898995</v>
       </c>
       <c r="J10" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K10" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008141266171982631</v>
+        <v>0.0006291539022346138</v>
       </c>
       <c r="M10" t="n">
-        <v>5.455117541392942</v>
+        <v>5.430221564866171</v>
       </c>
       <c r="N10" t="n">
-        <v>47.91903504023887</v>
+        <v>47.54705882850772</v>
       </c>
       <c r="O10" t="n">
-        <v>6.92235762152165</v>
+        <v>6.895437537133356</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6181091719836</v>
+        <v>356.6592973621367</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27223,28 +27496,28 @@
         <v>0.0873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4068208395186863</v>
+        <v>0.3943856339091708</v>
       </c>
       <c r="J11" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K11" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0954790375155552</v>
+        <v>0.09181877220205703</v>
       </c>
       <c r="M11" t="n">
-        <v>6.883521288847801</v>
+        <v>6.873355422311063</v>
       </c>
       <c r="N11" t="n">
-        <v>77.77805819594363</v>
+        <v>77.29877926291785</v>
       </c>
       <c r="O11" t="n">
-        <v>8.81918693508328</v>
+        <v>8.791972433016259</v>
       </c>
       <c r="P11" t="n">
-        <v>401.9957230649493</v>
+        <v>402.1364171860072</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27301,28 +27574,28 @@
         <v>0.1136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08861109488524385</v>
+        <v>0.0739483253558303</v>
       </c>
       <c r="J12" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K12" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01092600222377427</v>
+        <v>0.007702526564975498</v>
       </c>
       <c r="M12" t="n">
-        <v>4.833170492003045</v>
+        <v>4.837582887462444</v>
       </c>
       <c r="N12" t="n">
-        <v>35.21429965818164</v>
+        <v>35.35264991542114</v>
       </c>
       <c r="O12" t="n">
-        <v>5.934163770758408</v>
+        <v>5.945809441566483</v>
       </c>
       <c r="P12" t="n">
-        <v>363.8270702971357</v>
+        <v>363.9928051804058</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27379,28 +27652,28 @@
         <v>0.0838</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1391243884840009</v>
+        <v>0.1187920226024419</v>
       </c>
       <c r="J13" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K13" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02071416488003164</v>
+        <v>0.01524141787107747</v>
       </c>
       <c r="M13" t="n">
-        <v>5.727628786913288</v>
+        <v>5.744804115790683</v>
       </c>
       <c r="N13" t="n">
-        <v>45.99833215402654</v>
+        <v>46.41901635455016</v>
       </c>
       <c r="O13" t="n">
-        <v>6.782207026774289</v>
+        <v>6.813150251869553</v>
       </c>
       <c r="P13" t="n">
-        <v>364.9699842477648</v>
+        <v>365.1978323950354</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27457,28 +27730,28 @@
         <v>0.0814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1482513954660202</v>
+        <v>0.135211042937882</v>
       </c>
       <c r="J14" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K14" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02335034132030711</v>
+        <v>0.01977982401828859</v>
       </c>
       <c r="M14" t="n">
-        <v>5.577405704560909</v>
+        <v>5.571553683551014</v>
       </c>
       <c r="N14" t="n">
-        <v>45.54267118269446</v>
+        <v>45.46551811673928</v>
       </c>
       <c r="O14" t="n">
-        <v>6.748531038877606</v>
+        <v>6.742812329936172</v>
       </c>
       <c r="P14" t="n">
-        <v>362.7163306949286</v>
+        <v>362.8637291823113</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27535,28 +27808,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0778994169191277</v>
+        <v>0.06509165041500231</v>
       </c>
       <c r="J15" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K15" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00647957229488838</v>
+        <v>0.004602707077411949</v>
       </c>
       <c r="M15" t="n">
-        <v>5.708520395262007</v>
+        <v>5.697112455195734</v>
       </c>
       <c r="N15" t="n">
-        <v>46.09716587714045</v>
+        <v>45.98225763507845</v>
       </c>
       <c r="O15" t="n">
-        <v>6.789489367923073</v>
+        <v>6.781021872481938</v>
       </c>
       <c r="P15" t="n">
-        <v>365.3993746577576</v>
+        <v>365.5441570419658</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27613,28 +27886,28 @@
         <v>0.0959</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1500140192024097</v>
+        <v>0.1392511872128556</v>
       </c>
       <c r="J16" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K16" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02159588493173181</v>
+        <v>0.01899250282760834</v>
       </c>
       <c r="M16" t="n">
-        <v>6.026616851443933</v>
+        <v>6.00621045466371</v>
       </c>
       <c r="N16" t="n">
-        <v>50.51103989506465</v>
+        <v>50.26255309410865</v>
       </c>
       <c r="O16" t="n">
-        <v>7.107111923634286</v>
+        <v>7.089608811077565</v>
       </c>
       <c r="P16" t="n">
-        <v>370.3782114808988</v>
+        <v>370.4998576954871</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27691,28 +27964,28 @@
         <v>0.0883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2850692076986424</v>
+        <v>0.2724756329547007</v>
       </c>
       <c r="J17" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K17" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07606238240484964</v>
+        <v>0.07099146529951617</v>
       </c>
       <c r="M17" t="n">
-        <v>5.939014614565257</v>
+        <v>5.930237408182342</v>
       </c>
       <c r="N17" t="n">
-        <v>49.62115250055814</v>
+        <v>49.46361795410734</v>
       </c>
       <c r="O17" t="n">
-        <v>7.044228311217499</v>
+        <v>7.033037605054258</v>
       </c>
       <c r="P17" t="n">
-        <v>372.1611306677952</v>
+        <v>372.302235900132</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27769,28 +28042,28 @@
         <v>0.0919</v>
       </c>
       <c r="I18" t="n">
-        <v>0.237156528314777</v>
+        <v>0.2247876429718641</v>
       </c>
       <c r="J18" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K18" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05633386095619453</v>
+        <v>0.05167011686216172</v>
       </c>
       <c r="M18" t="n">
-        <v>5.808372792692944</v>
+        <v>5.798562671757116</v>
       </c>
       <c r="N18" t="n">
-        <v>47.36009085653359</v>
+        <v>47.21520010080365</v>
       </c>
       <c r="O18" t="n">
-        <v>6.881866814791869</v>
+        <v>6.87133175598469</v>
       </c>
       <c r="P18" t="n">
-        <v>363.711901652592</v>
+        <v>363.8504857817616</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27847,28 +28120,28 @@
         <v>0.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2314995434655371</v>
+        <v>0.2231429910848758</v>
       </c>
       <c r="J19" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K19" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05592539790472395</v>
+        <v>0.05312086186809495</v>
       </c>
       <c r="M19" t="n">
-        <v>5.692857827502555</v>
+        <v>5.665913367362554</v>
       </c>
       <c r="N19" t="n">
-        <v>45.47691683487426</v>
+        <v>45.186937795194</v>
       </c>
       <c r="O19" t="n">
-        <v>6.74365752651143</v>
+        <v>6.722123012500887</v>
       </c>
       <c r="P19" t="n">
-        <v>359.9734890496311</v>
+        <v>360.0670937834093</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27925,28 +28198,28 @@
         <v>0.1034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2319329651296606</v>
+        <v>0.2220339937714975</v>
       </c>
       <c r="J20" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K20" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05925813178771966</v>
+        <v>0.05547669853153914</v>
       </c>
       <c r="M20" t="n">
-        <v>5.539010776763027</v>
+        <v>5.515823435835184</v>
       </c>
       <c r="N20" t="n">
-        <v>42.92803230461578</v>
+        <v>42.73246891978921</v>
       </c>
       <c r="O20" t="n">
-        <v>6.551948740994223</v>
+        <v>6.537007642628943</v>
       </c>
       <c r="P20" t="n">
-        <v>365.544560489011</v>
+        <v>365.6554477322435</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28003,28 +28276,28 @@
         <v>0.0847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.126099041485194</v>
+        <v>0.1139610287570873</v>
       </c>
       <c r="J21" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K21" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01588574230067175</v>
+        <v>0.01321412955023693</v>
       </c>
       <c r="M21" t="n">
-        <v>5.881130696551547</v>
+        <v>5.855762692680802</v>
       </c>
       <c r="N21" t="n">
-        <v>49.51708673913368</v>
+        <v>49.37579025837469</v>
       </c>
       <c r="O21" t="n">
-        <v>7.036837836637539</v>
+        <v>7.026790893315005</v>
       </c>
       <c r="P21" t="n">
-        <v>377.7485611527389</v>
+        <v>377.8845314462365</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28081,28 +28354,28 @@
         <v>0.0767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04424391795096956</v>
+        <v>0.02901978890923358</v>
       </c>
       <c r="J22" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K22" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002337697687813778</v>
+        <v>0.001017327601743778</v>
       </c>
       <c r="M22" t="n">
-        <v>5.402277034275685</v>
+        <v>5.400344456816783</v>
       </c>
       <c r="N22" t="n">
-        <v>41.99483466224925</v>
+        <v>42.10198779787012</v>
       </c>
       <c r="O22" t="n">
-        <v>6.480342171695045</v>
+        <v>6.48860445688209</v>
       </c>
       <c r="P22" t="n">
-        <v>384.3574758374692</v>
+        <v>384.5280427547191</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28159,28 +28432,28 @@
         <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01810770159682295</v>
+        <v>0.0002813145969969671</v>
       </c>
       <c r="J23" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K23" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0004290082430503661</v>
+        <v>1.039970811689273e-07</v>
       </c>
       <c r="M23" t="n">
-        <v>5.142650791247606</v>
+        <v>5.169299892992656</v>
       </c>
       <c r="N23" t="n">
-        <v>38.40326679408241</v>
+        <v>38.7418463302899</v>
       </c>
       <c r="O23" t="n">
-        <v>6.197036936640156</v>
+        <v>6.224294846027933</v>
       </c>
       <c r="P23" t="n">
-        <v>378.1805731652673</v>
+        <v>378.3803007046037</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28237,28 +28510,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.05621255388320168</v>
+        <v>-0.06945434450111629</v>
       </c>
       <c r="J24" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K24" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002794715693653527</v>
+        <v>0.004325508122738464</v>
       </c>
       <c r="M24" t="n">
-        <v>6.201158005819969</v>
+        <v>6.192631091068948</v>
       </c>
       <c r="N24" t="n">
-        <v>56.67702886285477</v>
+        <v>56.53222233510213</v>
       </c>
       <c r="O24" t="n">
-        <v>7.528414764268422</v>
+        <v>7.518791281522724</v>
       </c>
       <c r="P24" t="n">
-        <v>385.803494487123</v>
+        <v>385.951830270744</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28296,7 +28569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y284"/>
+  <dimension ref="A1:Y287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64283,6 +64556,387 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:05:43+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>-36.260339130703755,175.4898373106193</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>-36.261068874456186,175.48999407699353</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>-36.26175431652587,175.49028748986748</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-36.2623888937372,175.4907377968465</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-36.26304450240675,175.49112380336499</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-36.26364758937436,175.49158698173463</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-36.26423047911461,175.49212615306513</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-36.264814892561574,175.49266767056284</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-36.26531616121886,175.49331713835642</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>-36.26550137401707,175.49437696262808</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-36.2663545803957,175.49457504241815</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>-36.2667918547634,175.4952884653704</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>-36.267177559630944,175.4960506816283</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-36.267552182384996,175.49681932551917</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>-36.26788416100975,175.49761680441753</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>-36.2681689023194,175.49841586227495</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>-36.26842929608046,175.49924792988816</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>-36.26863271754888,175.50011117445393</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>-36.268768915705884,175.50099420629138</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>-36.26888024303702,175.50187907455165</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>-36.268964915243984,175.5027376729756</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>-36.268993737421845,175.50362223978047</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>-36.26888357153974,175.50451233297122</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>-36.26034020211093,175.4898340054806</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>-36.261073561870724,175.48997961688218</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>-36.26175187236045,175.49029502984015</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-36.262384507591555,175.49075132756798</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-36.26303835256214,175.49113916198098</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-36.26364649791552,175.49158875226965</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-36.26422110325191,175.49213832666578</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-36.264799245370654,175.49268798684363</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-36.26529467727757,175.4933450329736</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-36.26550137401707,175.49437696262808</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-36.26633561101887,175.49459608296218</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-36.266785084843725,175.49529417692787</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-36.26716270451479,175.49606184411797</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-36.26754148359231,175.49682736478985</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-36.26785995245916,175.497633328435</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>-36.268144423397885,175.4984268242005</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>-36.26841036501344,175.49925350247776</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>-36.268603707414115,175.50011971373823</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>-36.26874691706249,175.50100068154495</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>-36.26884751902603,175.50188693118884</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>-36.26894447448215,175.50273852962712</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>-36.2689733514273,175.50362020431916</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>-36.26885348650884,175.50450932888324</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>-36.26033698788913,175.48984392089645</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>-36.261084309436235,175.48994646190576</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>-36.261751169244285,175.49029719887332</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-36.2623819964388,175.49075907416355</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-36.26304278524254,175.49112809180997</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-36.263636183628286,175.4916054838231</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-36.26422128952734,175.49213808480616</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-36.264784902109504,175.49270661009388</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-36.26526847431217,175.4933790547113</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-36.265516586763304,175.49435721077916</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-36.26631764708295,175.49461600827365</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-36.266775487924185,175.4953022735296</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-36.26714022941502,175.49607873243642</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-36.26752470418985,175.49683997313804</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-36.267848281886835,175.49764129440732</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>-36.26814425399358,175.49842690006156</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>-36.268399497178564,175.49925670155588</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>-36.26859476773501,175.50012234517814</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>-36.26872570721481,175.501006924615</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>-36.268829653484715,175.50189122048562</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>-36.268918991065355,175.50273959761097</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>-36.26894452365502,175.5036173259819</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>-36.2688269937202,175.5045066834948</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0122/nzd0122.xlsx
+++ b/data/nzd0122/nzd0122.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y287"/>
+  <dimension ref="A1:Y288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23682,6 +23682,87 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="C288" t="n">
+        <v>342</v>
+      </c>
+      <c r="D288" t="n">
+        <v>346.95</v>
+      </c>
+      <c r="E288" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="F288" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="G288" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="H288" t="n">
+        <v>360.51</v>
+      </c>
+      <c r="I288" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="J288" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="K288" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="L288" t="n">
+        <v>366.62</v>
+      </c>
+      <c r="M288" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="N288" t="n">
+        <v>367.19</v>
+      </c>
+      <c r="O288" t="n">
+        <v>368.36</v>
+      </c>
+      <c r="P288" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>380.48</v>
+      </c>
+      <c r="R288" t="n">
+        <v>370.28</v>
+      </c>
+      <c r="S288" t="n">
+        <v>369.38</v>
+      </c>
+      <c r="T288" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="U288" t="n">
+        <v>382.41</v>
+      </c>
+      <c r="V288" t="n">
+        <v>385.21</v>
+      </c>
+      <c r="W288" t="n">
+        <v>376.58</v>
+      </c>
+      <c r="X288" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23693,7 +23774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26626,6 +26707,16 @@
       </c>
       <c r="B293" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -26794,28 +26885,28 @@
         <v>0.1526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2162976064563276</v>
+        <v>0.2173515334591746</v>
       </c>
       <c r="J2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K2" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0618155308876287</v>
+        <v>0.06282228079369712</v>
       </c>
       <c r="M2" t="n">
-        <v>4.686325807317202</v>
+        <v>4.675470977279232</v>
       </c>
       <c r="N2" t="n">
-        <v>35.64667182084131</v>
+        <v>35.52882987745362</v>
       </c>
       <c r="O2" t="n">
-        <v>5.97048338251111</v>
+        <v>5.960606502483922</v>
       </c>
       <c r="P2" t="n">
-        <v>353.0044821078856</v>
+        <v>352.992507931155</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26872,28 +26963,28 @@
         <v>0.1234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1932667319874243</v>
+        <v>0.1882859441955975</v>
       </c>
       <c r="J3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05721118896039945</v>
+        <v>0.05458658658126236</v>
       </c>
       <c r="M3" t="n">
-        <v>4.689758155908865</v>
+        <v>4.695017179644443</v>
       </c>
       <c r="N3" t="n">
-        <v>30.90100308300362</v>
+        <v>30.95414802057576</v>
       </c>
       <c r="O3" t="n">
-        <v>5.558867068297606</v>
+        <v>5.563645209804069</v>
       </c>
       <c r="P3" t="n">
-        <v>343.6743494201362</v>
+        <v>343.7309385701587</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26950,28 +27041,28 @@
         <v>0.1286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1292129918410563</v>
+        <v>0.1280225909766381</v>
       </c>
       <c r="J4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K4" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01520323111302724</v>
+        <v>0.01503985167203736</v>
       </c>
       <c r="M4" t="n">
-        <v>6.063260585973384</v>
+        <v>6.046800923653811</v>
       </c>
       <c r="N4" t="n">
-        <v>54.29352100625245</v>
+        <v>54.11224632072555</v>
       </c>
       <c r="O4" t="n">
-        <v>7.368413737450717</v>
+        <v>7.356102658386814</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1406640813154</v>
+        <v>345.1541888038932</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27028,28 +27119,28 @@
         <v>0.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1118275268223622</v>
+        <v>0.1146024698812352</v>
       </c>
       <c r="J5" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K5" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01042982217081856</v>
+        <v>0.01102273016244593</v>
       </c>
       <c r="M5" t="n">
-        <v>6.295670248702931</v>
+        <v>6.289337486069511</v>
       </c>
       <c r="N5" t="n">
-        <v>59.56512535681492</v>
+        <v>59.40627497979791</v>
       </c>
       <c r="O5" t="n">
-        <v>7.71784460564055</v>
+        <v>7.707546625210768</v>
       </c>
       <c r="P5" t="n">
-        <v>352.9512997030873</v>
+        <v>352.9197722267873</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27106,28 +27197,28 @@
         <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1595183725551739</v>
+        <v>0.1577476871573706</v>
       </c>
       <c r="J6" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01946218674796718</v>
+        <v>0.01917927037967482</v>
       </c>
       <c r="M6" t="n">
-        <v>6.422506658269092</v>
+        <v>6.407215915858955</v>
       </c>
       <c r="N6" t="n">
-        <v>64.36044765669708</v>
+        <v>64.15504107335812</v>
       </c>
       <c r="O6" t="n">
-        <v>8.022496348188454</v>
+        <v>8.009684205595008</v>
       </c>
       <c r="P6" t="n">
-        <v>362.1338811031481</v>
+        <v>362.1539987202414</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27184,28 +27275,28 @@
         <v>0.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1432264248448274</v>
+        <v>0.1427223482707517</v>
       </c>
       <c r="J7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K7" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01860976619596655</v>
+        <v>0.01862125901376854</v>
       </c>
       <c r="M7" t="n">
-        <v>5.852571292706463</v>
+        <v>5.834220405222394</v>
       </c>
       <c r="N7" t="n">
-        <v>54.30902956492452</v>
+        <v>54.12012640778327</v>
       </c>
       <c r="O7" t="n">
-        <v>7.369466029837204</v>
+        <v>7.356638254514305</v>
       </c>
       <c r="P7" t="n">
-        <v>364.7748158210607</v>
+        <v>364.7805428799247</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27262,28 +27353,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1349249146978202</v>
+        <v>0.1369089366173103</v>
       </c>
       <c r="J8" t="n">
+        <v>287</v>
+      </c>
+      <c r="K8" t="n">
         <v>286</v>
       </c>
-      <c r="K8" t="n">
-        <v>285</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01695908150717396</v>
+        <v>0.01757725966628521</v>
       </c>
       <c r="M8" t="n">
-        <v>6.067267703402514</v>
+        <v>6.056909250586792</v>
       </c>
       <c r="N8" t="n">
-        <v>52.95539081252102</v>
+        <v>52.79582468549765</v>
       </c>
       <c r="O8" t="n">
-        <v>7.277045472753418</v>
+        <v>7.266073539780454</v>
       </c>
       <c r="P8" t="n">
-        <v>354.1908008413924</v>
+        <v>354.1682812708983</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27340,28 +27431,28 @@
         <v>0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1369343631424338</v>
+        <v>0.13813957653032</v>
       </c>
       <c r="J9" t="n">
+        <v>287</v>
+      </c>
+      <c r="K9" t="n">
         <v>286</v>
       </c>
-      <c r="K9" t="n">
-        <v>285</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01568398149985228</v>
+        <v>0.01607601086430077</v>
       </c>
       <c r="M9" t="n">
-        <v>6.332355904916044</v>
+        <v>6.316888899625327</v>
       </c>
       <c r="N9" t="n">
-        <v>59.05541546280696</v>
+        <v>58.85837184588611</v>
       </c>
       <c r="O9" t="n">
-        <v>7.684752140622816</v>
+        <v>7.671921001019634</v>
       </c>
       <c r="P9" t="n">
-        <v>349.3432136882598</v>
+        <v>349.3295339564068</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27418,28 +27509,28 @@
         <v>0.1145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02442297896898995</v>
+        <v>0.02960180002160167</v>
       </c>
       <c r="J10" t="n">
+        <v>287</v>
+      </c>
+      <c r="K10" t="n">
         <v>286</v>
       </c>
-      <c r="K10" t="n">
-        <v>285</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0006291539022346138</v>
+        <v>0.0009277351566637781</v>
       </c>
       <c r="M10" t="n">
-        <v>5.430221564866171</v>
+        <v>5.437493848099817</v>
       </c>
       <c r="N10" t="n">
-        <v>47.54705882850772</v>
+        <v>47.55518487418002</v>
       </c>
       <c r="O10" t="n">
-        <v>6.895437537133356</v>
+        <v>6.896026745465828</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6592973621367</v>
+        <v>356.6005153372884</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27496,28 +27587,28 @@
         <v>0.0873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3943856339091708</v>
+        <v>0.3907022759544079</v>
       </c>
       <c r="J11" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K11" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09181877220205703</v>
+        <v>0.09080608575269045</v>
       </c>
       <c r="M11" t="n">
-        <v>6.873355422311063</v>
+        <v>6.867868087716696</v>
       </c>
       <c r="N11" t="n">
-        <v>77.29877926291785</v>
+        <v>77.11600581475049</v>
       </c>
       <c r="O11" t="n">
-        <v>8.791972433016259</v>
+        <v>8.781571944404401</v>
       </c>
       <c r="P11" t="n">
-        <v>402.1364171860072</v>
+        <v>402.1782440216473</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27574,28 +27665,28 @@
         <v>0.1136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0739483253558303</v>
+        <v>0.07442528281854895</v>
       </c>
       <c r="J12" t="n">
+        <v>287</v>
+      </c>
+      <c r="K12" t="n">
         <v>286</v>
       </c>
-      <c r="K12" t="n">
-        <v>285</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.007702526564975498</v>
+        <v>0.007861097438913056</v>
       </c>
       <c r="M12" t="n">
-        <v>4.837582887462444</v>
+        <v>4.823389247242898</v>
       </c>
       <c r="N12" t="n">
-        <v>35.35264991542114</v>
+        <v>35.2305182932569</v>
       </c>
       <c r="O12" t="n">
-        <v>5.945809441566483</v>
+        <v>5.935530161094028</v>
       </c>
       <c r="P12" t="n">
-        <v>363.9928051804058</v>
+        <v>363.9873914916259</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27652,28 +27743,28 @@
         <v>0.0838</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1187920226024419</v>
+        <v>0.1151909846172803</v>
       </c>
       <c r="J13" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K13" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01524141787107747</v>
+        <v>0.01442673322770804</v>
       </c>
       <c r="M13" t="n">
-        <v>5.744804115790683</v>
+        <v>5.738270356361008</v>
       </c>
       <c r="N13" t="n">
-        <v>46.41901635455016</v>
+        <v>46.34343023286616</v>
       </c>
       <c r="O13" t="n">
-        <v>6.813150251869553</v>
+        <v>6.807600916098576</v>
       </c>
       <c r="P13" t="n">
-        <v>365.1978323950354</v>
+        <v>365.2383465901393</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27730,28 +27821,28 @@
         <v>0.0814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.135211042937882</v>
+        <v>0.135737642854744</v>
       </c>
       <c r="J14" t="n">
+        <v>287</v>
+      </c>
+      <c r="K14" t="n">
         <v>286</v>
       </c>
-      <c r="K14" t="n">
-        <v>285</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01977982401828859</v>
+        <v>0.02008172227408489</v>
       </c>
       <c r="M14" t="n">
-        <v>5.571553683551014</v>
+        <v>5.55494433328913</v>
       </c>
       <c r="N14" t="n">
-        <v>45.46551811673928</v>
+        <v>45.30835071978389</v>
       </c>
       <c r="O14" t="n">
-        <v>6.742812329936172</v>
+        <v>6.731147801065126</v>
       </c>
       <c r="P14" t="n">
-        <v>362.8637291823113</v>
+        <v>362.8577520286148</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27808,28 +27899,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06509165041500231</v>
+        <v>0.06588271183739346</v>
       </c>
       <c r="J15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K15" t="n">
         <v>286</v>
       </c>
-      <c r="K15" t="n">
-        <v>285</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.004602707077411949</v>
+        <v>0.004750681241196708</v>
       </c>
       <c r="M15" t="n">
-        <v>5.697112455195734</v>
+        <v>5.681731393077882</v>
       </c>
       <c r="N15" t="n">
-        <v>45.98225763507845</v>
+        <v>45.82554907853822</v>
       </c>
       <c r="O15" t="n">
-        <v>6.781021872481938</v>
+        <v>6.769457074133657</v>
       </c>
       <c r="P15" t="n">
-        <v>365.5441570419658</v>
+        <v>365.5351781273218</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27886,28 +27977,28 @@
         <v>0.0959</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1392511872128556</v>
+        <v>0.1420210527119651</v>
       </c>
       <c r="J16" t="n">
+        <v>287</v>
+      </c>
+      <c r="K16" t="n">
         <v>286</v>
       </c>
-      <c r="K16" t="n">
-        <v>285</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.01899250282760834</v>
+        <v>0.01987109177574342</v>
       </c>
       <c r="M16" t="n">
-        <v>6.00621045466371</v>
+        <v>6.000562863773589</v>
       </c>
       <c r="N16" t="n">
-        <v>50.26255309410865</v>
+        <v>50.13669129010202</v>
       </c>
       <c r="O16" t="n">
-        <v>7.089608811077565</v>
+        <v>7.080726748724457</v>
       </c>
       <c r="P16" t="n">
-        <v>370.4998576954871</v>
+        <v>370.4684184352885</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27964,28 +28055,28 @@
         <v>0.0883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2724756329547007</v>
+        <v>0.2731329470068319</v>
       </c>
       <c r="J17" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K17" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07099146529951617</v>
+        <v>0.07181538942090793</v>
       </c>
       <c r="M17" t="n">
-        <v>5.930237408182342</v>
+        <v>5.913109739336914</v>
       </c>
       <c r="N17" t="n">
-        <v>49.46361795410734</v>
+        <v>49.29414136196409</v>
       </c>
       <c r="O17" t="n">
-        <v>7.033037605054258</v>
+        <v>7.020978661266825</v>
       </c>
       <c r="P17" t="n">
-        <v>372.302235900132</v>
+        <v>372.2948406574651</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28042,28 +28133,28 @@
         <v>0.0919</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2247876429718641</v>
+        <v>0.2251028136787639</v>
       </c>
       <c r="J18" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K18" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05167011686216172</v>
+        <v>0.05218476715844089</v>
       </c>
       <c r="M18" t="n">
-        <v>5.798562671757116</v>
+        <v>5.780085705956776</v>
       </c>
       <c r="N18" t="n">
-        <v>47.21520010080365</v>
+        <v>47.05134714889105</v>
       </c>
       <c r="O18" t="n">
-        <v>6.87133175598469</v>
+        <v>6.859398453865401</v>
       </c>
       <c r="P18" t="n">
-        <v>363.8504857817616</v>
+        <v>363.8469398909482</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28120,28 +28211,28 @@
         <v>0.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2231429910848758</v>
+        <v>0.2255648013602911</v>
       </c>
       <c r="J19" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K19" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05312086186809495</v>
+        <v>0.05456710878033</v>
       </c>
       <c r="M19" t="n">
-        <v>5.665913367362554</v>
+        <v>5.659986866227293</v>
       </c>
       <c r="N19" t="n">
-        <v>45.186937795194</v>
+        <v>45.06845868726608</v>
       </c>
       <c r="O19" t="n">
-        <v>6.722123012500887</v>
+        <v>6.713304602598193</v>
       </c>
       <c r="P19" t="n">
-        <v>360.0670937834093</v>
+        <v>360.0398467245315</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28198,28 +28289,28 @@
         <v>0.1034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2220339937714975</v>
+        <v>0.2241398022591643</v>
       </c>
       <c r="J20" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K20" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05547669853153914</v>
+        <v>0.05684704541294283</v>
       </c>
       <c r="M20" t="n">
-        <v>5.515823435835184</v>
+        <v>5.509446294676734</v>
       </c>
       <c r="N20" t="n">
-        <v>42.73246891978921</v>
+        <v>42.61303652371087</v>
       </c>
       <c r="O20" t="n">
-        <v>6.537007642628943</v>
+        <v>6.527866153936589</v>
       </c>
       <c r="P20" t="n">
-        <v>365.6554477322435</v>
+        <v>365.6317559144198</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28276,28 +28367,28 @@
         <v>0.0847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1139610287570873</v>
+        <v>0.1150295728564818</v>
       </c>
       <c r="J21" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K21" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01321412955023693</v>
+        <v>0.01355985014543104</v>
       </c>
       <c r="M21" t="n">
-        <v>5.855762692680802</v>
+        <v>5.842382561429775</v>
       </c>
       <c r="N21" t="n">
-        <v>49.37579025837469</v>
+        <v>49.21133491712429</v>
       </c>
       <c r="O21" t="n">
-        <v>7.026790893315005</v>
+        <v>7.01507910982651</v>
       </c>
       <c r="P21" t="n">
-        <v>377.8845314462365</v>
+        <v>377.8725095780145</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28354,28 +28445,28 @@
         <v>0.0767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02901978890923358</v>
+        <v>0.0289567128383071</v>
       </c>
       <c r="J22" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K22" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001017327601743778</v>
+        <v>0.001020700383225881</v>
       </c>
       <c r="M22" t="n">
-        <v>5.400344456816783</v>
+        <v>5.381756801256075</v>
       </c>
       <c r="N22" t="n">
-        <v>42.10198779787012</v>
+        <v>41.95531740902219</v>
       </c>
       <c r="O22" t="n">
-        <v>6.48860445688209</v>
+        <v>6.477292444302804</v>
       </c>
       <c r="P22" t="n">
-        <v>384.5280427547191</v>
+        <v>384.5287524046184</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28432,28 +28523,28 @@
         <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0002813145969969671</v>
+        <v>-0.001017712589287902</v>
       </c>
       <c r="J23" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K23" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L23" t="n">
-        <v>1.039970811689273e-07</v>
+        <v>1.371164092378585e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>5.169299892992656</v>
+        <v>5.157131074651013</v>
       </c>
       <c r="N23" t="n">
-        <v>38.7418463302899</v>
+        <v>38.61806845209676</v>
       </c>
       <c r="O23" t="n">
-        <v>6.224294846027933</v>
+        <v>6.214343766810519</v>
       </c>
       <c r="P23" t="n">
-        <v>378.3803007046037</v>
+        <v>378.3949156687022</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28510,28 +28601,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.06945434450111629</v>
+        <v>-0.06820448591228045</v>
       </c>
       <c r="J24" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K24" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004325508122738464</v>
+        <v>0.004203071199878727</v>
       </c>
       <c r="M24" t="n">
-        <v>6.192631091068948</v>
+        <v>6.17766925226034</v>
       </c>
       <c r="N24" t="n">
-        <v>56.53222233510213</v>
+        <v>56.34562445564337</v>
       </c>
       <c r="O24" t="n">
-        <v>7.518791281522724</v>
+        <v>7.50637225666589</v>
       </c>
       <c r="P24" t="n">
-        <v>385.951830270744</v>
+        <v>385.9377684877445</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28569,7 +28660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y287"/>
+  <dimension ref="A1:Y288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64937,6 +65028,133 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>-36.26033993425916,175.48983483176528</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>-36.2610776466163,175.48996701592654</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>-36.26173781002995,175.4903384104952</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-36.262371750930555,175.49079068026808</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-36.26303268192455,175.49115332381942</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-36.26362395928502,175.49162531380657</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-36.26419769463609,175.4921687203447</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-36.2647668333222,175.49273007054228</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-36.26523898044236,175.49341734929405</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-36.265503547266725,175.49437414093583</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-36.266288154047274,175.4946487214519</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-36.26675376466267,175.495320600714</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-36.26711021129907,175.4961012887374</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-36.267487604772974,175.49686785029294</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-36.267796631713246,175.49767654918958</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-36.268096905489045,175.49844810321403</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>-36.26836058331766,175.4992681563128</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>-36.26854796588486,175.50013612153123</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>-36.268682586366644,175.5010196171282</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>-36.26879126910344,175.5019004360976</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>-36.26888234176968,175.502741133545</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>-36.26891524685174,175.50361440281355</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>-36.26878595234884,175.5045025853892</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0122/nzd0122.xlsx
+++ b/data/nzd0122/nzd0122.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y288"/>
+  <dimension ref="A1:Y290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23763,6 +23763,168 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="C289" t="n">
+        <v>339.09</v>
+      </c>
+      <c r="D289" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="E289" t="n">
+        <v>357.79</v>
+      </c>
+      <c r="F289" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="G289" t="n">
+        <v>365.59</v>
+      </c>
+      <c r="H289" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="I289" t="n">
+        <v>354.34</v>
+      </c>
+      <c r="J289" t="n">
+        <v>361.98</v>
+      </c>
+      <c r="K289" t="n">
+        <v>389.92</v>
+      </c>
+      <c r="L289" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="M289" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="N289" t="n">
+        <v>362.81</v>
+      </c>
+      <c r="O289" t="n">
+        <v>366.71</v>
+      </c>
+      <c r="P289" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="R289" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="S289" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="T289" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="U289" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="V289" t="n">
+        <v>385.71</v>
+      </c>
+      <c r="W289" t="n">
+        <v>372.87</v>
+      </c>
+      <c r="X289" t="n">
+        <v>377.51</v>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="C290" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="D290" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="E290" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="F290" t="n">
+        <v>359.66</v>
+      </c>
+      <c r="G290" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="H290" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="I290" t="n">
+        <v>351.38</v>
+      </c>
+      <c r="J290" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="K290" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="L290" t="n">
+        <v>362.41</v>
+      </c>
+      <c r="M290" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="N290" t="n">
+        <v>360.7</v>
+      </c>
+      <c r="O290" t="n">
+        <v>363.92</v>
+      </c>
+      <c r="P290" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>373.36</v>
+      </c>
+      <c r="R290" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="S290" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="T290" t="n">
+        <v>366.61</v>
+      </c>
+      <c r="U290" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="V290" t="n">
+        <v>383.95</v>
+      </c>
+      <c r="W290" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="X290" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23774,7 +23936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26717,6 +26879,26 @@
       </c>
       <c r="B294" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -26885,28 +27067,28 @@
         <v>0.1526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2173515334591746</v>
+        <v>0.2152445849953205</v>
       </c>
       <c r="J2" t="n">
+        <v>289</v>
+      </c>
+      <c r="K2" t="n">
         <v>287</v>
       </c>
-      <c r="K2" t="n">
-        <v>285</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.06282228079369712</v>
+        <v>0.06256735482790787</v>
       </c>
       <c r="M2" t="n">
-        <v>4.675470977279232</v>
+        <v>4.651743565417851</v>
       </c>
       <c r="N2" t="n">
-        <v>35.52882987745362</v>
+        <v>35.29705972810155</v>
       </c>
       <c r="O2" t="n">
-        <v>5.960606502483922</v>
+        <v>5.941132865716904</v>
       </c>
       <c r="P2" t="n">
-        <v>352.992507931155</v>
+        <v>353.016619074872</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26963,28 +27145,28 @@
         <v>0.1234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1882859441955975</v>
+        <v>0.1733285779455693</v>
       </c>
       <c r="J3" t="n">
+        <v>289</v>
+      </c>
+      <c r="K3" t="n">
         <v>287</v>
       </c>
-      <c r="K3" t="n">
-        <v>285</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05458658658126236</v>
+        <v>0.04630274579032068</v>
       </c>
       <c r="M3" t="n">
-        <v>4.695017179644443</v>
+        <v>4.726272515200319</v>
       </c>
       <c r="N3" t="n">
-        <v>30.95414802057576</v>
+        <v>31.46486816030211</v>
       </c>
       <c r="O3" t="n">
-        <v>5.563645209804069</v>
+        <v>5.609355413976022</v>
       </c>
       <c r="P3" t="n">
-        <v>343.7309385701587</v>
+        <v>343.9020670766613</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27041,28 +27223,28 @@
         <v>0.1286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1280225909766381</v>
+        <v>0.1215556926182039</v>
       </c>
       <c r="J4" t="n">
+        <v>289</v>
+      </c>
+      <c r="K4" t="n">
         <v>287</v>
       </c>
-      <c r="K4" t="n">
-        <v>285</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01503985167203736</v>
+        <v>0.01375365743549473</v>
       </c>
       <c r="M4" t="n">
-        <v>6.046800923653811</v>
+        <v>6.030177485302691</v>
       </c>
       <c r="N4" t="n">
-        <v>54.11224632072555</v>
+        <v>53.87652660112756</v>
       </c>
       <c r="O4" t="n">
-        <v>7.356102658386814</v>
+        <v>7.340063119696421</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1541888038932</v>
+        <v>345.2281868336424</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27119,28 +27301,28 @@
         <v>0.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1146024698812352</v>
+        <v>0.1155485039885239</v>
       </c>
       <c r="J5" t="n">
+        <v>289</v>
+      </c>
+      <c r="K5" t="n">
         <v>287</v>
       </c>
-      <c r="K5" t="n">
-        <v>285</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01102273016244593</v>
+        <v>0.01137518170806351</v>
       </c>
       <c r="M5" t="n">
-        <v>6.289337486069511</v>
+        <v>6.254274359581755</v>
       </c>
       <c r="N5" t="n">
-        <v>59.40627497979791</v>
+        <v>59.00429178707709</v>
       </c>
       <c r="O5" t="n">
-        <v>7.707546625210768</v>
+        <v>7.681425114331136</v>
       </c>
       <c r="P5" t="n">
-        <v>352.9197722267873</v>
+        <v>352.9089655908285</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27197,28 +27379,28 @@
         <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1577476871573706</v>
+        <v>0.149527770176472</v>
       </c>
       <c r="J6" t="n">
+        <v>289</v>
+      </c>
+      <c r="K6" t="n">
         <v>287</v>
       </c>
-      <c r="K6" t="n">
-        <v>285</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01917927037967482</v>
+        <v>0.01747174683077324</v>
       </c>
       <c r="M6" t="n">
-        <v>6.407215915858955</v>
+        <v>6.395313411043096</v>
       </c>
       <c r="N6" t="n">
-        <v>64.15504107335812</v>
+        <v>63.9343443146108</v>
       </c>
       <c r="O6" t="n">
-        <v>8.009684205595008</v>
+        <v>7.995895466713582</v>
       </c>
       <c r="P6" t="n">
-        <v>362.1539987202414</v>
+        <v>362.2480539424012</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27275,28 +27457,28 @@
         <v>0.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1427223482707517</v>
+        <v>0.136731963031473</v>
       </c>
       <c r="J7" t="n">
+        <v>289</v>
+      </c>
+      <c r="K7" t="n">
         <v>287</v>
       </c>
-      <c r="K7" t="n">
-        <v>285</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01862125901376854</v>
+        <v>0.01734193765376779</v>
       </c>
       <c r="M7" t="n">
-        <v>5.834220405222394</v>
+        <v>5.818885856969747</v>
       </c>
       <c r="N7" t="n">
-        <v>54.12012640778327</v>
+        <v>53.86748272906006</v>
       </c>
       <c r="O7" t="n">
-        <v>7.356638254514305</v>
+        <v>7.339447031558989</v>
       </c>
       <c r="P7" t="n">
-        <v>364.7805428799247</v>
+        <v>364.8490917431581</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27353,28 +27535,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1369089366173103</v>
+        <v>0.1374298909371668</v>
       </c>
       <c r="J8" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K8" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01757725966628521</v>
+        <v>0.01797741322507129</v>
       </c>
       <c r="M8" t="n">
-        <v>6.056909250586792</v>
+        <v>6.025199919675027</v>
       </c>
       <c r="N8" t="n">
-        <v>52.79582468549765</v>
+        <v>52.4444185792268</v>
       </c>
       <c r="O8" t="n">
-        <v>7.266073539780454</v>
+        <v>7.24185187498521</v>
       </c>
       <c r="P8" t="n">
-        <v>354.1682812708983</v>
+        <v>354.1623478360285</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27431,28 +27613,28 @@
         <v>0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.13813957653032</v>
+        <v>0.1378788592037724</v>
       </c>
       <c r="J9" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01607601086430077</v>
+        <v>0.01626002893153278</v>
       </c>
       <c r="M9" t="n">
-        <v>6.316888899625327</v>
+        <v>6.28313263621244</v>
       </c>
       <c r="N9" t="n">
-        <v>58.85837184588611</v>
+        <v>58.46513575415684</v>
       </c>
       <c r="O9" t="n">
-        <v>7.671921001019634</v>
+        <v>7.64624978366237</v>
       </c>
       <c r="P9" t="n">
-        <v>349.3295339564068</v>
+        <v>349.3325349867416</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27509,28 +27691,28 @@
         <v>0.1145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02960180002160167</v>
+        <v>0.03450186363382896</v>
       </c>
       <c r="J10" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K10" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0009277351566637781</v>
+        <v>0.001277307242556036</v>
       </c>
       <c r="M10" t="n">
-        <v>5.437493848099817</v>
+        <v>5.424050420908894</v>
       </c>
       <c r="N10" t="n">
-        <v>47.55518487418002</v>
+        <v>47.31264714557346</v>
       </c>
       <c r="O10" t="n">
-        <v>6.896026745465828</v>
+        <v>6.878418942284155</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6005153372884</v>
+        <v>356.5445293015971</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27587,28 +27769,28 @@
         <v>0.0873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3907022759544079</v>
+        <v>0.3603232144110842</v>
       </c>
       <c r="J11" t="n">
+        <v>289</v>
+      </c>
+      <c r="K11" t="n">
         <v>287</v>
       </c>
-      <c r="K11" t="n">
-        <v>285</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09080608575269045</v>
+        <v>0.07665296783603481</v>
       </c>
       <c r="M11" t="n">
-        <v>6.867868087716696</v>
+        <v>6.974881708211425</v>
       </c>
       <c r="N11" t="n">
-        <v>77.11600581475049</v>
+        <v>79.59114130397515</v>
       </c>
       <c r="O11" t="n">
-        <v>8.781571944404401</v>
+        <v>8.921386736599594</v>
       </c>
       <c r="P11" t="n">
-        <v>402.1782440216473</v>
+        <v>402.5255921371231</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27665,28 +27847,28 @@
         <v>0.1136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07442528281854895</v>
+        <v>0.07132668781327883</v>
       </c>
       <c r="J12" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K12" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007861097438913056</v>
+        <v>0.007328203534385014</v>
       </c>
       <c r="M12" t="n">
-        <v>4.823389247242898</v>
+        <v>4.801665056393144</v>
       </c>
       <c r="N12" t="n">
-        <v>35.2305182932569</v>
+        <v>35.0311883621188</v>
       </c>
       <c r="O12" t="n">
-        <v>5.935530161094028</v>
+        <v>5.91871509384586</v>
       </c>
       <c r="P12" t="n">
-        <v>363.9873914916259</v>
+        <v>364.0228262422492</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27743,28 +27925,28 @@
         <v>0.0838</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1151909846172803</v>
+        <v>0.1049296832794098</v>
       </c>
       <c r="J13" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K13" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01442673322770804</v>
+        <v>0.01209345367098569</v>
       </c>
       <c r="M13" t="n">
-        <v>5.738270356361008</v>
+        <v>5.73615234981524</v>
       </c>
       <c r="N13" t="n">
-        <v>46.34343023286616</v>
+        <v>46.3775393190826</v>
       </c>
       <c r="O13" t="n">
-        <v>6.807600916098576</v>
+        <v>6.810105676058383</v>
       </c>
       <c r="P13" t="n">
-        <v>365.2383465901393</v>
+        <v>365.3546179624763</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27821,28 +28003,28 @@
         <v>0.0814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.135737642854744</v>
+        <v>0.1288556670024845</v>
       </c>
       <c r="J14" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K14" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02008172227408489</v>
+        <v>0.0183488053666292</v>
       </c>
       <c r="M14" t="n">
-        <v>5.55494433328913</v>
+        <v>5.544466484991463</v>
       </c>
       <c r="N14" t="n">
-        <v>45.30835071978389</v>
+        <v>45.15429311529359</v>
       </c>
       <c r="O14" t="n">
-        <v>6.731147801065126</v>
+        <v>6.719694421273455</v>
       </c>
       <c r="P14" t="n">
-        <v>362.8577520286148</v>
+        <v>362.9364218438805</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27899,28 +28081,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06588271183739346</v>
+        <v>0.06299288076986534</v>
       </c>
       <c r="J15" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K15" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004750681241196708</v>
+        <v>0.004408992612705553</v>
       </c>
       <c r="M15" t="n">
-        <v>5.681731393077882</v>
+        <v>5.653098401599956</v>
       </c>
       <c r="N15" t="n">
-        <v>45.82554907853822</v>
+        <v>45.54777109114927</v>
       </c>
       <c r="O15" t="n">
-        <v>6.769457074133657</v>
+        <v>6.748908881526648</v>
       </c>
       <c r="P15" t="n">
-        <v>365.5351781273218</v>
+        <v>365.5682262848006</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27977,28 +28159,28 @@
         <v>0.0959</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1420210527119651</v>
+        <v>0.1386611808768745</v>
       </c>
       <c r="J16" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K16" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01987109177574342</v>
+        <v>0.01923216833032237</v>
       </c>
       <c r="M16" t="n">
-        <v>6.000562863773589</v>
+        <v>5.972127380632251</v>
       </c>
       <c r="N16" t="n">
-        <v>50.13669129010202</v>
+        <v>49.84141299274221</v>
       </c>
       <c r="O16" t="n">
-        <v>7.080726748724457</v>
+        <v>7.05984511110139</v>
       </c>
       <c r="P16" t="n">
-        <v>370.4684184352885</v>
+        <v>370.5068408153273</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28055,28 +28237,28 @@
         <v>0.0883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2731329470068319</v>
+        <v>0.2656112074533553</v>
       </c>
       <c r="J17" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K17" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07181538942090793</v>
+        <v>0.06891781442452194</v>
       </c>
       <c r="M17" t="n">
-        <v>5.913109739336914</v>
+        <v>5.903714651138122</v>
       </c>
       <c r="N17" t="n">
-        <v>49.29414136196409</v>
+        <v>49.14674656469693</v>
       </c>
       <c r="O17" t="n">
-        <v>7.020978661266825</v>
+        <v>7.010474061338287</v>
       </c>
       <c r="P17" t="n">
-        <v>372.2948406574651</v>
+        <v>372.3800735204</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28133,28 +28315,28 @@
         <v>0.0919</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2251028136787639</v>
+        <v>0.2158453333006692</v>
       </c>
       <c r="J18" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K18" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05218476715844089</v>
+        <v>0.0486184314440069</v>
       </c>
       <c r="M18" t="n">
-        <v>5.780085705956776</v>
+        <v>5.778151369776758</v>
       </c>
       <c r="N18" t="n">
-        <v>47.05134714889105</v>
+        <v>47.00938582493961</v>
       </c>
       <c r="O18" t="n">
-        <v>6.859398453865401</v>
+        <v>6.856339097866996</v>
       </c>
       <c r="P18" t="n">
-        <v>363.8469398909482</v>
+        <v>363.9518284506976</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28211,28 +28393,28 @@
         <v>0.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2255648013602911</v>
+        <v>0.2191565555883477</v>
       </c>
       <c r="J19" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K19" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05456710878033</v>
+        <v>0.05228026823249665</v>
       </c>
       <c r="M19" t="n">
-        <v>5.659986866227293</v>
+        <v>5.645641977794328</v>
       </c>
       <c r="N19" t="n">
-        <v>45.06845868726608</v>
+        <v>44.89484828313459</v>
       </c>
       <c r="O19" t="n">
-        <v>6.713304602598193</v>
+        <v>6.700361802405493</v>
       </c>
       <c r="P19" t="n">
-        <v>360.0398467245315</v>
+        <v>360.1124587450357</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28289,28 +28471,28 @@
         <v>0.1034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2241398022591643</v>
+        <v>0.2180191656503514</v>
       </c>
       <c r="J20" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K20" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05684704541294283</v>
+        <v>0.05459084795808189</v>
       </c>
       <c r="M20" t="n">
-        <v>5.509446294676734</v>
+        <v>5.492799145826599</v>
       </c>
       <c r="N20" t="n">
-        <v>42.61303652371087</v>
+        <v>42.44580443289859</v>
       </c>
       <c r="O20" t="n">
-        <v>6.527866153936589</v>
+        <v>6.515044468988573</v>
       </c>
       <c r="P20" t="n">
-        <v>365.6317559144198</v>
+        <v>365.7011113241301</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28367,28 +28549,28 @@
         <v>0.0847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1150295728564818</v>
+        <v>0.1089127277175767</v>
       </c>
       <c r="J21" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K21" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01355985014543104</v>
+        <v>0.01232942059259456</v>
       </c>
       <c r="M21" t="n">
-        <v>5.842382561429775</v>
+        <v>5.820395970242885</v>
       </c>
       <c r="N21" t="n">
-        <v>49.21133491712429</v>
+        <v>48.99730348671977</v>
       </c>
       <c r="O21" t="n">
-        <v>7.01507910982651</v>
+        <v>6.999807389258634</v>
       </c>
       <c r="P21" t="n">
-        <v>377.8725095780145</v>
+        <v>377.9418206101104</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28445,28 +28627,28 @@
         <v>0.0767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0289567128383071</v>
+        <v>0.02826902281206809</v>
       </c>
       <c r="J22" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K22" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001020700383225881</v>
+        <v>0.0009878586733755856</v>
       </c>
       <c r="M22" t="n">
-        <v>5.381756801256075</v>
+        <v>5.349778632567424</v>
       </c>
       <c r="N22" t="n">
-        <v>41.95531740902219</v>
+        <v>41.67187118244406</v>
       </c>
       <c r="O22" t="n">
-        <v>6.477292444302804</v>
+        <v>6.455375371149541</v>
       </c>
       <c r="P22" t="n">
-        <v>384.5287524046184</v>
+        <v>384.5365561676043</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28523,28 +28705,28 @@
         <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.001017712589287902</v>
+        <v>-0.01005123740887834</v>
       </c>
       <c r="J23" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K23" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L23" t="n">
-        <v>1.371164092378585e-06</v>
+        <v>0.0001348535383457472</v>
       </c>
       <c r="M23" t="n">
-        <v>5.157131074651013</v>
+        <v>5.161104012748014</v>
       </c>
       <c r="N23" t="n">
-        <v>38.61806845209676</v>
+        <v>38.6245654309628</v>
       </c>
       <c r="O23" t="n">
-        <v>6.214343766810519</v>
+        <v>6.214866485368997</v>
       </c>
       <c r="P23" t="n">
-        <v>378.3949156687022</v>
+        <v>378.4972735286195</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28601,28 +28783,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.06820448591228045</v>
+        <v>-0.07994507625378779</v>
       </c>
       <c r="J24" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K24" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004203071199878727</v>
+        <v>0.005806377967885856</v>
       </c>
       <c r="M24" t="n">
-        <v>6.17766925226034</v>
+        <v>6.185167443260032</v>
       </c>
       <c r="N24" t="n">
-        <v>56.34562445564337</v>
+        <v>56.42798889509363</v>
       </c>
       <c r="O24" t="n">
-        <v>7.50637225666589</v>
+        <v>7.511856554480632</v>
       </c>
       <c r="P24" t="n">
-        <v>385.9377684877445</v>
+        <v>386.0708075896151</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28660,7 +28842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y288"/>
+  <dimension ref="A1:Y290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65155,6 +65337,260 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-36.26034790284742,175.48981024979332</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>-36.26108738973376,175.48993695954317</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>-36.261744104598804,175.49031899248976</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-36.2623782464498,175.49077064241197</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-36.26304134761657,175.49113168213586</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-36.26363656563896,175.491604864136</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-36.26420309662499,175.4921617064204</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-36.26476875817604,175.49272757131976</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-36.26525406888665,175.49339775859534</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-36.265613327340475,175.49423160496403</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-36.266297068988465,175.4946388331529</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-36.26676239445178,175.4953133200529</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-36.26714392395211,175.49607595627512</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-36.26750030478147,175.49685830728637</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>-36.26783219542152,175.49765227452755</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>-36.26814010358813,175.4984287586573</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>-36.268417727095084,175.49925133535987</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>-36.26861045599535,175.50011772725873</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>-36.268738327950636,175.5010032097307</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>-36.268836021400446,175.50188969162753</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>-36.26887783939919,175.50274132223464</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>-36.26894856493152,175.50361772948696</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>-36.26886076079994,175.50451005524454</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>-36.2603509496593,175.48980085080265</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>-36.26109150795648,175.48992425529627</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>-36.26175036568289,175.49029967776826</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-36.26238588035485,175.4907470927622</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-36.26304985356869,175.49111043937248</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-36.263648626260235,175.49158529972632</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-36.26422091697648,175.49213856852535</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-36.26478713742312,175.49270370776964</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-36.265268971050936,175.49337840974968</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-36.26559109813001,175.49426046691826</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-36.26631637352021,175.4946174208887</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-36.2667777941607,175.4953003278348</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-36.267160164520746,175.49606375272978</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-36.26752177933977,175.496842170923</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>-36.2678564828296,175.49763569669727</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>-36.26815721342273,175.49842109669</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>-36.268423599231625,175.49924960682512</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>-36.26862149912823,175.5001144766552</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>-36.26875173748238,175.50099926266498</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>-36.268847784355856,175.5018868674864</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>-36.2688936877433,175.50274065804703</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>-36.26896311352688,175.50361918210558</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>-36.26888949873982,175.50451292482174</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0122/nzd0122.xlsx
+++ b/data/nzd0122/nzd0122.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y290"/>
+  <dimension ref="A1:Y293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23925,6 +23925,249 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="C291" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="D291" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="E291" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="F291" t="n">
+        <v>359.66</v>
+      </c>
+      <c r="G291" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="H291" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="I291" t="n">
+        <v>351.38</v>
+      </c>
+      <c r="J291" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="K291" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="L291" t="n">
+        <v>362.41</v>
+      </c>
+      <c r="M291" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="N291" t="n">
+        <v>360.7</v>
+      </c>
+      <c r="O291" t="n">
+        <v>363.92</v>
+      </c>
+      <c r="P291" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="R291" t="n">
+        <v>360.76</v>
+      </c>
+      <c r="S291" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="T291" t="n">
+        <v>366.61</v>
+      </c>
+      <c r="U291" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="V291" t="n">
+        <v>383.95</v>
+      </c>
+      <c r="W291" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="X291" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>356.88</v>
+      </c>
+      <c r="C292" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="D292" t="n">
+        <v>343.51</v>
+      </c>
+      <c r="E292" t="n">
+        <v>355.01</v>
+      </c>
+      <c r="F292" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="G292" t="n">
+        <v>363.81</v>
+      </c>
+      <c r="H292" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="I292" t="n">
+        <v>351.59</v>
+      </c>
+      <c r="J292" t="n">
+        <v>359.15</v>
+      </c>
+      <c r="K292" t="n">
+        <v>399.75</v>
+      </c>
+      <c r="L292" t="n">
+        <v>362.05</v>
+      </c>
+      <c r="M292" t="n">
+        <v>359.59</v>
+      </c>
+      <c r="N292" t="n">
+        <v>360.65</v>
+      </c>
+      <c r="O292" t="n">
+        <v>363.98</v>
+      </c>
+      <c r="P292" t="n">
+        <v>370.77</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>369.43</v>
+      </c>
+      <c r="R292" t="n">
+        <v>361.86</v>
+      </c>
+      <c r="S292" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="T292" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="U292" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="V292" t="n">
+        <v>383.85</v>
+      </c>
+      <c r="W292" t="n">
+        <v>372.07</v>
+      </c>
+      <c r="X292" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="C293" t="n">
+        <v>338.84</v>
+      </c>
+      <c r="D293" t="n">
+        <v>342.14</v>
+      </c>
+      <c r="E293" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="F293" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="G293" t="n">
+        <v>362.86</v>
+      </c>
+      <c r="H293" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="I293" t="n">
+        <v>350</v>
+      </c>
+      <c r="J293" t="n">
+        <v>357.88</v>
+      </c>
+      <c r="K293" t="n">
+        <v>400.67</v>
+      </c>
+      <c r="L293" t="n">
+        <v>360.33</v>
+      </c>
+      <c r="M293" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="N293" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="O293" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="P293" t="n">
+        <v>369.28</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="R293" t="n">
+        <v>361.96</v>
+      </c>
+      <c r="S293" t="n">
+        <v>357.23</v>
+      </c>
+      <c r="T293" t="n">
+        <v>366.61</v>
+      </c>
+      <c r="U293" t="n">
+        <v>376.21</v>
+      </c>
+      <c r="V293" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="W293" t="n">
+        <v>371.16</v>
+      </c>
+      <c r="X293" t="n">
+        <v>373.09</v>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23936,7 +24179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26899,6 +27142,36 @@
       </c>
       <c r="B296" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -27067,28 +27340,28 @@
         <v>0.1526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2152445849953205</v>
+        <v>0.210926096282721</v>
       </c>
       <c r="J2" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K2" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06256735482790787</v>
+        <v>0.06146947094366428</v>
       </c>
       <c r="M2" t="n">
-        <v>4.651743565417851</v>
+        <v>4.621454536409171</v>
       </c>
       <c r="N2" t="n">
-        <v>35.29705972810155</v>
+        <v>34.97380056864214</v>
       </c>
       <c r="O2" t="n">
-        <v>5.941132865716904</v>
+        <v>5.913865112482879</v>
       </c>
       <c r="P2" t="n">
-        <v>353.016619074872</v>
+        <v>353.0661716700319</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27145,28 +27418,28 @@
         <v>0.1234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733285779455693</v>
+        <v>0.1522979618491534</v>
       </c>
       <c r="J3" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K3" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04630274579032068</v>
+        <v>0.03583855122816437</v>
       </c>
       <c r="M3" t="n">
-        <v>4.726272515200319</v>
+        <v>4.766578608409634</v>
       </c>
       <c r="N3" t="n">
-        <v>31.46486816030211</v>
+        <v>32.12778394451127</v>
       </c>
       <c r="O3" t="n">
-        <v>5.609355413976022</v>
+        <v>5.668137608113557</v>
       </c>
       <c r="P3" t="n">
-        <v>343.9020670766613</v>
+        <v>344.1433509429634</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27223,28 +27496,28 @@
         <v>0.1286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1215556926182039</v>
+        <v>0.109787352329209</v>
       </c>
       <c r="J4" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K4" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01375365743549473</v>
+        <v>0.01143893447333322</v>
       </c>
       <c r="M4" t="n">
-        <v>6.030177485302691</v>
+        <v>6.014152360296502</v>
       </c>
       <c r="N4" t="n">
-        <v>53.87652660112756</v>
+        <v>53.63099113395544</v>
       </c>
       <c r="O4" t="n">
-        <v>7.340063119696421</v>
+        <v>7.323318314395151</v>
       </c>
       <c r="P4" t="n">
-        <v>345.2281868336424</v>
+        <v>345.3632228550092</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27301,28 +27574,28 @@
         <v>0.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1155485039885239</v>
+        <v>0.1127052693701656</v>
       </c>
       <c r="J5" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K5" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01137518170806351</v>
+        <v>0.0110710927535036</v>
       </c>
       <c r="M5" t="n">
-        <v>6.254274359581755</v>
+        <v>6.200587046430105</v>
       </c>
       <c r="N5" t="n">
-        <v>59.00429178707709</v>
+        <v>58.41929283013575</v>
       </c>
       <c r="O5" t="n">
-        <v>7.681425114331136</v>
+        <v>7.643251456686202</v>
       </c>
       <c r="P5" t="n">
-        <v>352.9089655908285</v>
+        <v>352.9416097342328</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27379,28 +27652,28 @@
         <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.149527770176472</v>
+        <v>0.135683430624074</v>
       </c>
       <c r="J6" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K6" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01747174683077324</v>
+        <v>0.01466175360505551</v>
       </c>
       <c r="M6" t="n">
-        <v>6.395313411043096</v>
+        <v>6.384065688756358</v>
       </c>
       <c r="N6" t="n">
-        <v>63.9343443146108</v>
+        <v>63.70101105899884</v>
       </c>
       <c r="O6" t="n">
-        <v>7.995895466713582</v>
+        <v>7.981291315257128</v>
       </c>
       <c r="P6" t="n">
-        <v>362.2480539424012</v>
+        <v>362.4069004361284</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27457,28 +27730,28 @@
         <v>0.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.136731963031473</v>
+        <v>0.1257540406972184</v>
       </c>
       <c r="J7" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K7" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01734193765376779</v>
+        <v>0.01496868163279708</v>
       </c>
       <c r="M7" t="n">
-        <v>5.818885856969747</v>
+        <v>5.804479149096431</v>
       </c>
       <c r="N7" t="n">
-        <v>53.86748272906006</v>
+        <v>53.58011664396848</v>
       </c>
       <c r="O7" t="n">
-        <v>7.339447031558989</v>
+        <v>7.319844031396331</v>
       </c>
       <c r="P7" t="n">
-        <v>364.8490917431581</v>
+        <v>364.9750529923946</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27535,28 +27808,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1374298909371668</v>
+        <v>0.1344621717215179</v>
       </c>
       <c r="J8" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K8" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01797741322507129</v>
+        <v>0.01760666336656824</v>
       </c>
       <c r="M8" t="n">
-        <v>6.025199919675027</v>
+        <v>5.975054776418557</v>
       </c>
       <c r="N8" t="n">
-        <v>52.4444185792268</v>
+        <v>51.92674549169125</v>
       </c>
       <c r="O8" t="n">
-        <v>7.24185187498521</v>
+        <v>7.206021474551075</v>
       </c>
       <c r="P8" t="n">
-        <v>354.1623478360285</v>
+        <v>354.1963770815614</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27613,28 +27886,28 @@
         <v>0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1378788592037724</v>
+        <v>0.1335272618691035</v>
       </c>
       <c r="J9" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01626002893153278</v>
+        <v>0.01560066619584166</v>
       </c>
       <c r="M9" t="n">
-        <v>6.28313263621244</v>
+        <v>6.235765136971155</v>
       </c>
       <c r="N9" t="n">
-        <v>58.46513575415684</v>
+        <v>57.90960031258901</v>
       </c>
       <c r="O9" t="n">
-        <v>7.64624978366237</v>
+        <v>7.609835761209897</v>
       </c>
       <c r="P9" t="n">
-        <v>349.3325349867416</v>
+        <v>349.3824291614551</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27691,28 +27964,28 @@
         <v>0.1145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03450186363382896</v>
+        <v>0.03745499552239245</v>
       </c>
       <c r="J10" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K10" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001277307242556036</v>
+        <v>0.00153895577986829</v>
       </c>
       <c r="M10" t="n">
-        <v>5.424050420908894</v>
+        <v>5.382639676208637</v>
       </c>
       <c r="N10" t="n">
-        <v>47.31264714557346</v>
+        <v>46.8497197293774</v>
       </c>
       <c r="O10" t="n">
-        <v>6.878418942284155</v>
+        <v>6.844685509895791</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5445293015971</v>
+        <v>356.5107002132805</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27769,28 +28042,28 @@
         <v>0.0873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3603232144110842</v>
+        <v>0.3301550334064428</v>
       </c>
       <c r="J11" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K11" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07665296783603481</v>
+        <v>0.06491931556708264</v>
       </c>
       <c r="M11" t="n">
-        <v>6.974881708211425</v>
+        <v>7.057444360248395</v>
       </c>
       <c r="N11" t="n">
-        <v>79.59114130397515</v>
+        <v>80.90302124774666</v>
       </c>
       <c r="O11" t="n">
-        <v>8.921386736599594</v>
+        <v>8.994610677941912</v>
       </c>
       <c r="P11" t="n">
-        <v>402.5255921371231</v>
+        <v>402.8714765535004</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27847,28 +28120,28 @@
         <v>0.1136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07132668781327883</v>
+        <v>0.06212074641326281</v>
       </c>
       <c r="J12" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K12" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007328203534385014</v>
+        <v>0.005664692335037302</v>
       </c>
       <c r="M12" t="n">
-        <v>4.801665056393144</v>
+        <v>4.786919369756144</v>
       </c>
       <c r="N12" t="n">
-        <v>35.0311883621188</v>
+        <v>34.86682312371788</v>
       </c>
       <c r="O12" t="n">
-        <v>5.91871509384586</v>
+        <v>5.904813555373098</v>
       </c>
       <c r="P12" t="n">
-        <v>364.0228262422492</v>
+        <v>364.1283670084121</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27925,28 +28198,28 @@
         <v>0.0838</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1049296832794098</v>
+        <v>0.08661819922822406</v>
       </c>
       <c r="J13" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K13" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01209345367098569</v>
+        <v>0.00832359519567305</v>
       </c>
       <c r="M13" t="n">
-        <v>5.73615234981524</v>
+        <v>5.745542569698295</v>
       </c>
       <c r="N13" t="n">
-        <v>46.3775393190826</v>
+        <v>46.66672747437894</v>
       </c>
       <c r="O13" t="n">
-        <v>6.810105676058383</v>
+        <v>6.831304961307096</v>
       </c>
       <c r="P13" t="n">
-        <v>365.3546179624763</v>
+        <v>365.5626989893497</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28003,28 +28276,28 @@
         <v>0.0814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1288556670024845</v>
+        <v>0.1160365134944541</v>
       </c>
       <c r="J14" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K14" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0183488053666292</v>
+        <v>0.01514913357735248</v>
       </c>
       <c r="M14" t="n">
-        <v>5.544466484991463</v>
+        <v>5.539459844628297</v>
       </c>
       <c r="N14" t="n">
-        <v>45.15429311529359</v>
+        <v>45.05619708729145</v>
       </c>
       <c r="O14" t="n">
-        <v>6.719694421273455</v>
+        <v>6.712391309160354</v>
       </c>
       <c r="P14" t="n">
-        <v>362.9364218438805</v>
+        <v>363.0833645073772</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28081,28 +28354,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06299288076986534</v>
+        <v>0.05506579841584373</v>
       </c>
       <c r="J15" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K15" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004408992612705553</v>
+        <v>0.00343956898056863</v>
       </c>
       <c r="M15" t="n">
-        <v>5.653098401599956</v>
+        <v>5.624283777706234</v>
       </c>
       <c r="N15" t="n">
-        <v>45.54777109114927</v>
+        <v>45.2216090189008</v>
       </c>
       <c r="O15" t="n">
-        <v>6.748908881526648</v>
+        <v>6.724701407415856</v>
       </c>
       <c r="P15" t="n">
-        <v>365.5682262848006</v>
+        <v>365.6591001253423</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28159,28 +28432,28 @@
         <v>0.0959</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1386611808768745</v>
+        <v>0.1300248470977682</v>
       </c>
       <c r="J16" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K16" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01923216833032237</v>
+        <v>0.01727757785518835</v>
       </c>
       <c r="M16" t="n">
-        <v>5.972127380632251</v>
+        <v>5.944006977592124</v>
       </c>
       <c r="N16" t="n">
-        <v>49.84141299274221</v>
+        <v>49.49749541224675</v>
       </c>
       <c r="O16" t="n">
-        <v>7.05984511110139</v>
+        <v>7.035445644182517</v>
       </c>
       <c r="P16" t="n">
-        <v>370.5068408153273</v>
+        <v>370.6058433664725</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28237,28 +28510,28 @@
         <v>0.0883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2656112074533553</v>
+        <v>0.2432710270615255</v>
       </c>
       <c r="J17" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K17" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L17" t="n">
-        <v>0.06891781442452194</v>
+        <v>0.05844221726519661</v>
       </c>
       <c r="M17" t="n">
-        <v>5.903714651138122</v>
+        <v>5.935231966947557</v>
       </c>
       <c r="N17" t="n">
-        <v>49.14674656469693</v>
+        <v>49.77727143034193</v>
       </c>
       <c r="O17" t="n">
-        <v>7.010474061338287</v>
+        <v>7.055300945412742</v>
       </c>
       <c r="P17" t="n">
-        <v>372.3800735204</v>
+        <v>372.6339127596265</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28315,28 +28588,28 @@
         <v>0.0919</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2158453333006692</v>
+        <v>0.1986267184490666</v>
       </c>
       <c r="J18" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K18" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0486184314440069</v>
+        <v>0.04181067133186811</v>
       </c>
       <c r="M18" t="n">
-        <v>5.778151369776758</v>
+        <v>5.789807510300943</v>
       </c>
       <c r="N18" t="n">
-        <v>47.00938582493961</v>
+        <v>47.2029934092153</v>
       </c>
       <c r="O18" t="n">
-        <v>6.856339097866996</v>
+        <v>6.870443465251373</v>
       </c>
       <c r="P18" t="n">
-        <v>363.9518284506976</v>
+        <v>364.1474631547536</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28393,28 +28666,28 @@
         <v>0.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2191565555883477</v>
+        <v>0.2003535543324496</v>
       </c>
       <c r="J19" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K19" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05228026823249665</v>
+        <v>0.04427454936383146</v>
       </c>
       <c r="M19" t="n">
-        <v>5.645641977794328</v>
+        <v>5.660198728486908</v>
       </c>
       <c r="N19" t="n">
-        <v>44.89484828313459</v>
+        <v>45.23797131308713</v>
       </c>
       <c r="O19" t="n">
-        <v>6.700361802405493</v>
+        <v>6.725917878853943</v>
       </c>
       <c r="P19" t="n">
-        <v>360.1124587450357</v>
+        <v>360.3261010999391</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28471,28 +28744,28 @@
         <v>0.1034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2180191656503514</v>
+        <v>0.2082726886961406</v>
       </c>
       <c r="J20" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K20" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05459084795808189</v>
+        <v>0.05089952111138363</v>
       </c>
       <c r="M20" t="n">
-        <v>5.492799145826599</v>
+        <v>5.470361148625577</v>
       </c>
       <c r="N20" t="n">
-        <v>42.44580443289859</v>
+        <v>42.22728504239055</v>
       </c>
       <c r="O20" t="n">
-        <v>6.515044468988573</v>
+        <v>6.498252460653599</v>
       </c>
       <c r="P20" t="n">
-        <v>365.7011113241301</v>
+        <v>365.8118576463022</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28549,28 +28822,28 @@
         <v>0.0847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1089127277175767</v>
+        <v>0.09991534539315888</v>
       </c>
       <c r="J21" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K21" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01232942059259456</v>
+        <v>0.01059253951454864</v>
       </c>
       <c r="M21" t="n">
-        <v>5.820395970242885</v>
+        <v>5.788051652902382</v>
       </c>
       <c r="N21" t="n">
-        <v>48.99730348671977</v>
+        <v>48.68212110811987</v>
       </c>
       <c r="O21" t="n">
-        <v>6.999807389258634</v>
+        <v>6.977257420227512</v>
       </c>
       <c r="P21" t="n">
-        <v>377.9418206101104</v>
+        <v>378.0440545016766</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28627,28 +28900,28 @@
         <v>0.0767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02826902281206809</v>
+        <v>0.02436461688041555</v>
       </c>
       <c r="J22" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K22" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0009878586733755856</v>
+        <v>0.0007501603550508218</v>
       </c>
       <c r="M22" t="n">
-        <v>5.349778632567424</v>
+        <v>5.308842720662547</v>
       </c>
       <c r="N22" t="n">
-        <v>41.67187118244406</v>
+        <v>41.2828021861683</v>
       </c>
       <c r="O22" t="n">
-        <v>6.455375371149541</v>
+        <v>6.425169428596284</v>
       </c>
       <c r="P22" t="n">
-        <v>384.5365561676043</v>
+        <v>384.5809367227722</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28705,28 +28978,28 @@
         <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.01005123740887834</v>
+        <v>-0.02413856325974109</v>
       </c>
       <c r="J23" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K23" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0001348535383457472</v>
+        <v>0.0007858201869550552</v>
       </c>
       <c r="M23" t="n">
-        <v>5.161104012748014</v>
+        <v>5.169856638491578</v>
       </c>
       <c r="N23" t="n">
-        <v>38.6245654309628</v>
+        <v>38.68015964088714</v>
       </c>
       <c r="O23" t="n">
-        <v>6.214866485368997</v>
+        <v>6.219337556435343</v>
       </c>
       <c r="P23" t="n">
-        <v>378.4972735286195</v>
+        <v>378.6573434670206</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28783,28 +29056,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.07994507625378779</v>
+        <v>-0.1018739598185219</v>
       </c>
       <c r="J24" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K24" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L24" t="n">
-        <v>0.005806377967885856</v>
+        <v>0.009425761368382579</v>
       </c>
       <c r="M24" t="n">
-        <v>6.185167443260032</v>
+        <v>6.219604963990507</v>
       </c>
       <c r="N24" t="n">
-        <v>56.42798889509363</v>
+        <v>56.94124780643082</v>
       </c>
       <c r="O24" t="n">
-        <v>7.511856554480632</v>
+        <v>7.545942473040118</v>
       </c>
       <c r="P24" t="n">
-        <v>386.0708075896151</v>
+        <v>386.3199786619303</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28842,7 +29115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y290"/>
+  <dimension ref="A1:Y293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65591,6 +65864,387 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>-36.2603509496593,175.48980085080265</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>-36.26109150795648,175.48992425529627</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>-36.26175036568289,175.49029967776826</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-36.26238588035485,175.4907470927622</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-36.26304985356869,175.49111043937248</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-36.263648626260235,175.49158529972632</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-36.26422091697648,175.49213856852535</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>-36.26478713742312,175.49270370776964</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>-36.265268971050936,175.49337840974968</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-36.26559109813001,175.49426046691826</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-36.26631637352021,175.4946174208887</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-36.2667777941607,175.4953003278348</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-36.267160164520746,175.49606375272978</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-36.26752177933977,175.496842170923</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>-36.2678564828296,175.49763569669727</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>-36.26819905628387,175.49840235899447</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>-36.26844402024358,175.49924359565014</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>-36.26866058831234,175.50010297054402</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>-36.26875173748238,175.50099926266498</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>-36.268847784355856,175.5018868674864</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>-36.2688936877433,175.50274065804703</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>-36.26896311352688,175.50361918210558</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>-36.26889758128538,175.50451373189082</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>-36.26035108358508,175.48980043766016</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>-36.261086920992874,175.48993840555494</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>-36.26174932774938,175.4903028796742</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-36.26238755445624,175.49074192836468</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-36.263047657196424,175.49111592459352</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-36.26364627962374,175.49158910637667</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-36.26421973723209,175.4921401003027</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-36.26478583349019,175.49270540079215</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-36.265271641021734,175.49337494308074</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-36.26555229013552,175.49431085436885</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-36.26631878658643,175.49461474435492</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-36.26678181147587,175.49529693855968</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-36.26716054936832,175.49606346354616</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-36.26752131752133,175.49684251794164</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>-36.267853722896966,175.49763758054215</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>-36.26819050136711,175.49840618998235</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>-36.26843437942251,175.49924643354424</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>-36.2686538397313,175.50010495702583</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>-36.268743937166555,175.50100155867068</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>-36.26883478319461,175.5018899889055</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>-36.26889458821738,175.50274062030908</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>-36.26895574942307,175.50361844682942</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>-36.268893989042915,175.50451337319342</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>-36.2603523223985,175.4897966160923</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>-36.261088226771,175.48993437737929</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>-36.26175391474527,175.4902887293151</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-36.26239254327711,175.49072653845866</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-36.26305109152387,175.4911073477023</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-36.26365146405305,175.4915806963349</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-36.264227871258875,175.4921295391</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-36.264795706124644,175.49269258219175</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-36.265279526748905,175.49336470431288</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-36.265546577597064,175.49431827139733</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-36.26633031567987,175.4946019564691</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-36.26678947413234,175.4952904738303</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-36.267167861472316,175.49605796905726</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-36.26753140055703,175.4968349413667</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-36.267865472324296,175.49762956074457</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-36.26819676932593,175.49840338312</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>-36.26843350298422,175.49924669153458</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>-36.26865445323866,175.5001047764366</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>-36.26875173748238,175.50099926266498</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>-36.26884610393365,175.50188727093519</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>-36.26890674461768,175.50274011084696</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>-36.26896392178217,175.50361926280664</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>-36.26890045507935,175.50451401884877</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
